--- a/backend/uploads/plantillas/plantilla-enfermeria.xlsx
+++ b/backend/uploads/plantillas/plantilla-enfermeria.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\OneDrive\Documentos\GITHUB\NHPanamericano\backend\uploads\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A316B5-DD0D-4A06-BB4B-5E9BA0569C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B06782-07B9-4E21-9D17-0FB68231C570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A7CB566D-D21A-42AF-A38C-A62178775491}"/>
   </bookViews>
@@ -598,6 +598,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -607,6 +625,57 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -616,9 +685,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -643,90 +709,36 @@
     <xf numFmtId="20" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -755,18 +767,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1146,7 +1146,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:L230"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
@@ -1187,29 +1187,29 @@
       <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="20"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="43"/>
       <c r="G4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="31"/>
-      <c r="I4" s="32"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="31"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
@@ -1219,192 +1219,192 @@
         <v>1</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="35"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="34"/>
       <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="21"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="28" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="45"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="54"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="48"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="57"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="48"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="57"/>
     </row>
     <row r="9" spans="1:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="51"/>
+      <c r="A9" s="44"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="60"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="30" t="s">
+      <c r="A10" s="44"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="53"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="36"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="55"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="38"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="55"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="38"/>
     </row>
     <row r="13" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="57"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="40"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="30" t="s">
+      <c r="A14" s="44"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="52"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="59"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="63"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="48"/>
+      <c r="A15" s="44"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="57"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="48"/>
+      <c r="A16" s="44"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="57"/>
     </row>
     <row r="17" spans="1:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="48"/>
+      <c r="A17" s="44"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="57"/>
     </row>
     <row r="18" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
-      <c r="B18" s="26"/>
+      <c r="A18" s="44"/>
+      <c r="B18" s="48"/>
       <c r="C18" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="60"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="62"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="66"/>
     </row>
     <row r="19" spans="1:9" ht="94.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="22"/>
-      <c r="B19" s="26"/>
+      <c r="A19" s="44"/>
+      <c r="B19" s="48"/>
       <c r="C19" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="63"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="65"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="69"/>
     </row>
     <row r="20" spans="1:9" ht="84" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="23"/>
-      <c r="B20" s="27"/>
+      <c r="A20" s="45"/>
+      <c r="B20" s="49"/>
       <c r="C20" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="67"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="71"/>
     </row>
     <row r="21" spans="1:9" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
@@ -1418,70 +1418,70 @@
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="21"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="69"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="42"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="27"/>
     </row>
     <row r="24" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="42"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="27"/>
     </row>
     <row r="25" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="42"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="27"/>
     </row>
     <row r="26" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="37"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="42"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="27"/>
     </row>
     <row r="27" spans="1:9" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="39"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="71"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="29"/>
     </row>
     <row r="28" spans="1:9" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12"/>
@@ -1495,70 +1495,70 @@
       <c r="I28" s="14"/>
     </row>
     <row r="29" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="21"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="69"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="25"/>
     </row>
     <row r="30" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="42"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="27"/>
     </row>
     <row r="31" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="37"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="42"/>
+      <c r="A31" s="16"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="27"/>
     </row>
     <row r="32" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="42"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="27"/>
     </row>
     <row r="33" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="42"/>
+      <c r="A33" s="16"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="27"/>
     </row>
     <row r="34" spans="1:9" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="39"/>
-      <c r="B34" s="40"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="71"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="29"/>
     </row>
     <row r="35" spans="1:9" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12"/>
@@ -1572,70 +1572,70 @@
       <c r="I35" s="14"/>
     </row>
     <row r="36" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="21"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="69"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="25"/>
     </row>
     <row r="37" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="42"/>
+      <c r="A37" s="16"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="27"/>
     </row>
     <row r="38" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="37"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="42"/>
+      <c r="A38" s="16"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="27"/>
     </row>
     <row r="39" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="37"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="42"/>
+      <c r="A39" s="16"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="27"/>
     </row>
     <row r="40" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="37"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="42"/>
+      <c r="A40" s="16"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="27"/>
     </row>
     <row r="41" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="39"/>
-      <c r="B41" s="40"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="71"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="29"/>
     </row>
     <row r="42" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12"/>
@@ -1649,70 +1649,70 @@
       <c r="I42" s="14"/>
     </row>
     <row r="43" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="21"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
-      <c r="H43" s="68"/>
-      <c r="I43" s="69"/>
+      <c r="A43" s="15"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="25"/>
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="37"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="42"/>
+      <c r="A44" s="16"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="27"/>
     </row>
     <row r="45" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="37"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="42"/>
+      <c r="A45" s="16"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="27"/>
     </row>
     <row r="46" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="37"/>
-      <c r="B46" s="38"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="42"/>
+      <c r="A46" s="16"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="27"/>
     </row>
     <row r="47" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="37"/>
-      <c r="B47" s="38"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="41"/>
-      <c r="I47" s="42"/>
+      <c r="A47" s="16"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="27"/>
     </row>
     <row r="48" spans="1:9" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="39"/>
-      <c r="B48" s="40"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
-      <c r="I48" s="71"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="29"/>
     </row>
     <row r="49" spans="1:9" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="12"/>
@@ -1726,70 +1726,70 @@
       <c r="I49" s="14"/>
     </row>
     <row r="50" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="21"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="68"/>
-      <c r="E50" s="68"/>
-      <c r="F50" s="68"/>
-      <c r="G50" s="68"/>
-      <c r="H50" s="68"/>
-      <c r="I50" s="69"/>
+      <c r="A50" s="15"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="25"/>
     </row>
     <row r="51" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="37"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="41"/>
-      <c r="I51" s="42"/>
+      <c r="A51" s="16"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="27"/>
     </row>
     <row r="52" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
-      <c r="B52" s="38"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="42"/>
+      <c r="A52" s="16"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="27"/>
     </row>
     <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="37"/>
-      <c r="B53" s="38"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="42"/>
+      <c r="A53" s="16"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="27"/>
     </row>
     <row r="54" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="37"/>
-      <c r="B54" s="38"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="42"/>
+      <c r="A54" s="16"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="27"/>
     </row>
     <row r="55" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="39"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="70"/>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="70"/>
-      <c r="I55" s="71"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="29"/>
     </row>
     <row r="56" spans="1:9" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="12"/>
@@ -1803,70 +1803,70 @@
       <c r="I56" s="14"/>
     </row>
     <row r="57" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="21"/>
-      <c r="B57" s="36"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="68"/>
-      <c r="E57" s="68"/>
-      <c r="F57" s="68"/>
-      <c r="G57" s="68"/>
-      <c r="H57" s="68"/>
-      <c r="I57" s="69"/>
+      <c r="A57" s="15"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="25"/>
     </row>
     <row r="58" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="37"/>
-      <c r="B58" s="38"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="41"/>
-      <c r="G58" s="41"/>
-      <c r="H58" s="41"/>
-      <c r="I58" s="42"/>
+      <c r="A58" s="16"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="27"/>
     </row>
     <row r="59" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="37"/>
-      <c r="B59" s="38"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="41"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="41"/>
-      <c r="H59" s="41"/>
-      <c r="I59" s="42"/>
+      <c r="A59" s="16"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="27"/>
     </row>
     <row r="60" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="37"/>
-      <c r="B60" s="38"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="41"/>
-      <c r="E60" s="41"/>
-      <c r="F60" s="41"/>
-      <c r="G60" s="41"/>
-      <c r="H60" s="41"/>
-      <c r="I60" s="42"/>
+      <c r="A60" s="16"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="27"/>
     </row>
     <row r="61" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="37"/>
-      <c r="B61" s="38"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="41"/>
-      <c r="E61" s="41"/>
-      <c r="F61" s="41"/>
-      <c r="G61" s="41"/>
-      <c r="H61" s="41"/>
-      <c r="I61" s="42"/>
+      <c r="A61" s="16"/>
+      <c r="B61" s="19"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="27"/>
     </row>
     <row r="62" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="39"/>
-      <c r="B62" s="40"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="70"/>
-      <c r="E62" s="70"/>
-      <c r="F62" s="70"/>
-      <c r="G62" s="70"/>
-      <c r="H62" s="70"/>
-      <c r="I62" s="71"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="23"/>
+      <c r="D62" s="28"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="29"/>
     </row>
     <row r="63" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="12"/>
@@ -1880,70 +1880,70 @@
       <c r="I63" s="14"/>
     </row>
     <row r="64" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="21"/>
-      <c r="B64" s="36"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="68"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="68"/>
-      <c r="H64" s="68"/>
-      <c r="I64" s="69"/>
+      <c r="A64" s="15"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="24"/>
+      <c r="I64" s="25"/>
     </row>
     <row r="65" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="37"/>
-      <c r="B65" s="38"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="41"/>
-      <c r="E65" s="41"/>
-      <c r="F65" s="41"/>
-      <c r="G65" s="41"/>
-      <c r="H65" s="41"/>
-      <c r="I65" s="42"/>
+      <c r="A65" s="16"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="27"/>
     </row>
     <row r="66" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="37"/>
-      <c r="B66" s="38"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="41"/>
-      <c r="E66" s="41"/>
-      <c r="F66" s="41"/>
-      <c r="G66" s="41"/>
-      <c r="H66" s="41"/>
-      <c r="I66" s="42"/>
+      <c r="A66" s="16"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="27"/>
     </row>
     <row r="67" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="37"/>
-      <c r="B67" s="38"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="41"/>
-      <c r="E67" s="41"/>
-      <c r="F67" s="41"/>
-      <c r="G67" s="41"/>
-      <c r="H67" s="41"/>
-      <c r="I67" s="42"/>
+      <c r="A67" s="16"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
+      <c r="I67" s="27"/>
     </row>
     <row r="68" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="37"/>
-      <c r="B68" s="38"/>
-      <c r="C68" s="16"/>
-      <c r="D68" s="41"/>
-      <c r="E68" s="41"/>
-      <c r="F68" s="41"/>
-      <c r="G68" s="41"/>
-      <c r="H68" s="41"/>
-      <c r="I68" s="42"/>
+      <c r="A68" s="16"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="27"/>
     </row>
     <row r="69" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="39"/>
-      <c r="B69" s="40"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="70"/>
-      <c r="E69" s="70"/>
-      <c r="F69" s="70"/>
-      <c r="G69" s="70"/>
-      <c r="H69" s="70"/>
-      <c r="I69" s="71"/>
+      <c r="A69" s="17"/>
+      <c r="B69" s="20"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="29"/>
     </row>
     <row r="70" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="12"/>
@@ -1957,70 +1957,70 @@
       <c r="I70" s="14"/>
     </row>
     <row r="71" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="21"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="68"/>
-      <c r="E71" s="68"/>
-      <c r="F71" s="68"/>
-      <c r="G71" s="68"/>
-      <c r="H71" s="68"/>
-      <c r="I71" s="69"/>
+      <c r="A71" s="15"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="24"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="24"/>
+      <c r="H71" s="24"/>
+      <c r="I71" s="25"/>
     </row>
     <row r="72" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
-      <c r="B72" s="38"/>
-      <c r="C72" s="16"/>
-      <c r="D72" s="41"/>
-      <c r="E72" s="41"/>
-      <c r="F72" s="41"/>
-      <c r="G72" s="41"/>
-      <c r="H72" s="41"/>
-      <c r="I72" s="42"/>
+      <c r="A72" s="16"/>
+      <c r="B72" s="19"/>
+      <c r="C72" s="22"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="27"/>
     </row>
     <row r="73" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
-      <c r="B73" s="38"/>
-      <c r="C73" s="16"/>
-      <c r="D73" s="41"/>
-      <c r="E73" s="41"/>
-      <c r="F73" s="41"/>
-      <c r="G73" s="41"/>
-      <c r="H73" s="41"/>
-      <c r="I73" s="42"/>
+      <c r="A73" s="16"/>
+      <c r="B73" s="19"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="27"/>
     </row>
     <row r="74" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="37"/>
-      <c r="B74" s="38"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="41"/>
-      <c r="E74" s="41"/>
-      <c r="F74" s="41"/>
-      <c r="G74" s="41"/>
-      <c r="H74" s="41"/>
-      <c r="I74" s="42"/>
+      <c r="A74" s="16"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="27"/>
     </row>
     <row r="75" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
-      <c r="B75" s="38"/>
-      <c r="C75" s="16"/>
-      <c r="D75" s="41"/>
-      <c r="E75" s="41"/>
-      <c r="F75" s="41"/>
-      <c r="G75" s="41"/>
-      <c r="H75" s="41"/>
-      <c r="I75" s="42"/>
+      <c r="A75" s="16"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="22"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="26"/>
+      <c r="I75" s="27"/>
     </row>
     <row r="76" spans="1:9" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="39"/>
-      <c r="B76" s="40"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="70"/>
-      <c r="E76" s="70"/>
-      <c r="F76" s="70"/>
-      <c r="G76" s="70"/>
-      <c r="H76" s="70"/>
-      <c r="I76" s="71"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="23"/>
+      <c r="D76" s="28"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="28"/>
+      <c r="G76" s="28"/>
+      <c r="H76" s="28"/>
+      <c r="I76" s="29"/>
     </row>
     <row r="77" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="12"/>
@@ -2034,70 +2034,70 @@
       <c r="I77" s="14"/>
     </row>
     <row r="78" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="21"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="15"/>
-      <c r="D78" s="68"/>
-      <c r="E78" s="68"/>
-      <c r="F78" s="68"/>
-      <c r="G78" s="68"/>
-      <c r="H78" s="68"/>
-      <c r="I78" s="69"/>
+      <c r="A78" s="15"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="37"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="41"/>
-      <c r="E79" s="41"/>
-      <c r="F79" s="41"/>
-      <c r="G79" s="41"/>
-      <c r="H79" s="41"/>
-      <c r="I79" s="42"/>
+      <c r="A79" s="16"/>
+      <c r="B79" s="19"/>
+      <c r="C79" s="22"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
+      <c r="I79" s="27"/>
     </row>
     <row r="80" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="37"/>
-      <c r="B80" s="38"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="41"/>
-      <c r="E80" s="41"/>
-      <c r="F80" s="41"/>
-      <c r="G80" s="41"/>
-      <c r="H80" s="41"/>
-      <c r="I80" s="42"/>
+      <c r="A80" s="16"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="22"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="27"/>
     </row>
     <row r="81" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="37"/>
-      <c r="B81" s="38"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="41"/>
-      <c r="E81" s="41"/>
-      <c r="F81" s="41"/>
-      <c r="G81" s="41"/>
-      <c r="H81" s="41"/>
-      <c r="I81" s="42"/>
+      <c r="A81" s="16"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="22"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="27"/>
     </row>
     <row r="82" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="37"/>
-      <c r="B82" s="38"/>
-      <c r="C82" s="16"/>
-      <c r="D82" s="41"/>
-      <c r="E82" s="41"/>
-      <c r="F82" s="41"/>
-      <c r="G82" s="41"/>
-      <c r="H82" s="41"/>
-      <c r="I82" s="42"/>
+      <c r="A82" s="16"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="22"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="26"/>
+      <c r="G82" s="26"/>
+      <c r="H82" s="26"/>
+      <c r="I82" s="27"/>
     </row>
     <row r="83" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="39"/>
-      <c r="B83" s="40"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="70"/>
-      <c r="E83" s="70"/>
-      <c r="F83" s="70"/>
-      <c r="G83" s="70"/>
-      <c r="H83" s="70"/>
-      <c r="I83" s="71"/>
+      <c r="A83" s="17"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="23"/>
+      <c r="D83" s="28"/>
+      <c r="E83" s="28"/>
+      <c r="F83" s="28"/>
+      <c r="G83" s="28"/>
+      <c r="H83" s="28"/>
+      <c r="I83" s="29"/>
     </row>
     <row r="84" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="12"/>
@@ -2111,70 +2111,70 @@
       <c r="I84" s="14"/>
     </row>
     <row r="85" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="21"/>
-      <c r="B85" s="36"/>
-      <c r="C85" s="15"/>
-      <c r="D85" s="68"/>
-      <c r="E85" s="68"/>
-      <c r="F85" s="68"/>
-      <c r="G85" s="68"/>
-      <c r="H85" s="68"/>
-      <c r="I85" s="69"/>
+      <c r="A85" s="15"/>
+      <c r="B85" s="18"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="24"/>
+      <c r="E85" s="24"/>
+      <c r="F85" s="24"/>
+      <c r="G85" s="24"/>
+      <c r="H85" s="24"/>
+      <c r="I85" s="25"/>
     </row>
     <row r="86" spans="1:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="37"/>
-      <c r="B86" s="38"/>
-      <c r="C86" s="16"/>
-      <c r="D86" s="41"/>
-      <c r="E86" s="41"/>
-      <c r="F86" s="41"/>
-      <c r="G86" s="41"/>
-      <c r="H86" s="41"/>
-      <c r="I86" s="42"/>
+      <c r="A86" s="16"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="22"/>
+      <c r="D86" s="26"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="26"/>
+      <c r="G86" s="26"/>
+      <c r="H86" s="26"/>
+      <c r="I86" s="27"/>
     </row>
     <row r="87" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="37"/>
-      <c r="B87" s="38"/>
-      <c r="C87" s="16"/>
-      <c r="D87" s="41"/>
-      <c r="E87" s="41"/>
-      <c r="F87" s="41"/>
-      <c r="G87" s="41"/>
-      <c r="H87" s="41"/>
-      <c r="I87" s="42"/>
+      <c r="A87" s="16"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="22"/>
+      <c r="D87" s="26"/>
+      <c r="E87" s="26"/>
+      <c r="F87" s="26"/>
+      <c r="G87" s="26"/>
+      <c r="H87" s="26"/>
+      <c r="I87" s="27"/>
     </row>
     <row r="88" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="37"/>
-      <c r="B88" s="38"/>
-      <c r="C88" s="16"/>
-      <c r="D88" s="41"/>
-      <c r="E88" s="41"/>
-      <c r="F88" s="41"/>
-      <c r="G88" s="41"/>
-      <c r="H88" s="41"/>
-      <c r="I88" s="42"/>
+      <c r="A88" s="16"/>
+      <c r="B88" s="19"/>
+      <c r="C88" s="22"/>
+      <c r="D88" s="26"/>
+      <c r="E88" s="26"/>
+      <c r="F88" s="26"/>
+      <c r="G88" s="26"/>
+      <c r="H88" s="26"/>
+      <c r="I88" s="27"/>
     </row>
     <row r="89" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="37"/>
-      <c r="B89" s="38"/>
-      <c r="C89" s="16"/>
-      <c r="D89" s="41"/>
-      <c r="E89" s="41"/>
-      <c r="F89" s="41"/>
-      <c r="G89" s="41"/>
-      <c r="H89" s="41"/>
-      <c r="I89" s="42"/>
+      <c r="A89" s="16"/>
+      <c r="B89" s="19"/>
+      <c r="C89" s="22"/>
+      <c r="D89" s="26"/>
+      <c r="E89" s="26"/>
+      <c r="F89" s="26"/>
+      <c r="G89" s="26"/>
+      <c r="H89" s="26"/>
+      <c r="I89" s="27"/>
     </row>
     <row r="90" spans="1:9" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="39"/>
-      <c r="B90" s="40"/>
-      <c r="C90" s="17"/>
-      <c r="D90" s="70"/>
-      <c r="E90" s="70"/>
-      <c r="F90" s="70"/>
-      <c r="G90" s="70"/>
-      <c r="H90" s="70"/>
-      <c r="I90" s="71"/>
+      <c r="A90" s="17"/>
+      <c r="B90" s="20"/>
+      <c r="C90" s="23"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28"/>
+      <c r="F90" s="28"/>
+      <c r="G90" s="28"/>
+      <c r="H90" s="28"/>
+      <c r="I90" s="29"/>
     </row>
     <row r="91" spans="1:9" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="12"/>
@@ -2188,70 +2188,70 @@
       <c r="I91" s="14"/>
     </row>
     <row r="92" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="21"/>
-      <c r="B92" s="36"/>
-      <c r="C92" s="15"/>
-      <c r="D92" s="68"/>
-      <c r="E92" s="68"/>
-      <c r="F92" s="68"/>
-      <c r="G92" s="68"/>
-      <c r="H92" s="68"/>
-      <c r="I92" s="69"/>
+      <c r="A92" s="15"/>
+      <c r="B92" s="18"/>
+      <c r="C92" s="21"/>
+      <c r="D92" s="24"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="25"/>
     </row>
     <row r="93" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="37"/>
-      <c r="B93" s="38"/>
-      <c r="C93" s="16"/>
-      <c r="D93" s="41"/>
-      <c r="E93" s="41"/>
-      <c r="F93" s="41"/>
-      <c r="G93" s="41"/>
-      <c r="H93" s="41"/>
-      <c r="I93" s="42"/>
+      <c r="A93" s="16"/>
+      <c r="B93" s="19"/>
+      <c r="C93" s="22"/>
+      <c r="D93" s="26"/>
+      <c r="E93" s="26"/>
+      <c r="F93" s="26"/>
+      <c r="G93" s="26"/>
+      <c r="H93" s="26"/>
+      <c r="I93" s="27"/>
     </row>
     <row r="94" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="37"/>
-      <c r="B94" s="38"/>
-      <c r="C94" s="16"/>
-      <c r="D94" s="41"/>
-      <c r="E94" s="41"/>
-      <c r="F94" s="41"/>
-      <c r="G94" s="41"/>
-      <c r="H94" s="41"/>
-      <c r="I94" s="42"/>
+      <c r="A94" s="16"/>
+      <c r="B94" s="19"/>
+      <c r="C94" s="22"/>
+      <c r="D94" s="26"/>
+      <c r="E94" s="26"/>
+      <c r="F94" s="26"/>
+      <c r="G94" s="26"/>
+      <c r="H94" s="26"/>
+      <c r="I94" s="27"/>
     </row>
     <row r="95" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="37"/>
-      <c r="B95" s="38"/>
-      <c r="C95" s="16"/>
-      <c r="D95" s="41"/>
-      <c r="E95" s="41"/>
-      <c r="F95" s="41"/>
-      <c r="G95" s="41"/>
-      <c r="H95" s="41"/>
-      <c r="I95" s="42"/>
+      <c r="A95" s="16"/>
+      <c r="B95" s="19"/>
+      <c r="C95" s="22"/>
+      <c r="D95" s="26"/>
+      <c r="E95" s="26"/>
+      <c r="F95" s="26"/>
+      <c r="G95" s="26"/>
+      <c r="H95" s="26"/>
+      <c r="I95" s="27"/>
     </row>
     <row r="96" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="37"/>
-      <c r="B96" s="38"/>
-      <c r="C96" s="16"/>
-      <c r="D96" s="41"/>
-      <c r="E96" s="41"/>
-      <c r="F96" s="41"/>
-      <c r="G96" s="41"/>
-      <c r="H96" s="41"/>
-      <c r="I96" s="42"/>
+      <c r="A96" s="16"/>
+      <c r="B96" s="19"/>
+      <c r="C96" s="22"/>
+      <c r="D96" s="26"/>
+      <c r="E96" s="26"/>
+      <c r="F96" s="26"/>
+      <c r="G96" s="26"/>
+      <c r="H96" s="26"/>
+      <c r="I96" s="27"/>
     </row>
     <row r="97" spans="1:9" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="39"/>
-      <c r="B97" s="40"/>
-      <c r="C97" s="17"/>
-      <c r="D97" s="70"/>
-      <c r="E97" s="70"/>
-      <c r="F97" s="70"/>
-      <c r="G97" s="70"/>
-      <c r="H97" s="70"/>
-      <c r="I97" s="71"/>
+      <c r="A97" s="17"/>
+      <c r="B97" s="20"/>
+      <c r="C97" s="23"/>
+      <c r="D97" s="28"/>
+      <c r="E97" s="28"/>
+      <c r="F97" s="28"/>
+      <c r="G97" s="28"/>
+      <c r="H97" s="28"/>
+      <c r="I97" s="29"/>
     </row>
     <row r="98" spans="1:9" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="12"/>
@@ -2265,204 +2265,1559 @@
       <c r="I98" s="14"/>
     </row>
     <row r="99" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="21"/>
-      <c r="B99" s="36"/>
-      <c r="C99" s="15"/>
-      <c r="D99" s="68"/>
-      <c r="E99" s="68"/>
-      <c r="F99" s="68"/>
-      <c r="G99" s="68"/>
-      <c r="H99" s="68"/>
-      <c r="I99" s="69"/>
+      <c r="A99" s="15"/>
+      <c r="B99" s="18"/>
+      <c r="C99" s="21"/>
+      <c r="D99" s="24"/>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="24"/>
+      <c r="H99" s="24"/>
+      <c r="I99" s="25"/>
     </row>
     <row r="100" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="37"/>
-      <c r="B100" s="38"/>
-      <c r="C100" s="16"/>
-      <c r="D100" s="41"/>
-      <c r="E100" s="41"/>
-      <c r="F100" s="41"/>
-      <c r="G100" s="41"/>
-      <c r="H100" s="41"/>
-      <c r="I100" s="42"/>
+      <c r="A100" s="16"/>
+      <c r="B100" s="19"/>
+      <c r="C100" s="22"/>
+      <c r="D100" s="26"/>
+      <c r="E100" s="26"/>
+      <c r="F100" s="26"/>
+      <c r="G100" s="26"/>
+      <c r="H100" s="26"/>
+      <c r="I100" s="27"/>
     </row>
     <row r="101" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="37"/>
-      <c r="B101" s="38"/>
-      <c r="C101" s="16"/>
-      <c r="D101" s="41"/>
-      <c r="E101" s="41"/>
-      <c r="F101" s="41"/>
-      <c r="G101" s="41"/>
-      <c r="H101" s="41"/>
-      <c r="I101" s="42"/>
+      <c r="A101" s="16"/>
+      <c r="B101" s="19"/>
+      <c r="C101" s="22"/>
+      <c r="D101" s="26"/>
+      <c r="E101" s="26"/>
+      <c r="F101" s="26"/>
+      <c r="G101" s="26"/>
+      <c r="H101" s="26"/>
+      <c r="I101" s="27"/>
     </row>
     <row r="102" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="37"/>
-      <c r="B102" s="38"/>
-      <c r="C102" s="16"/>
-      <c r="D102" s="41"/>
-      <c r="E102" s="41"/>
-      <c r="F102" s="41"/>
-      <c r="G102" s="41"/>
-      <c r="H102" s="41"/>
-      <c r="I102" s="42"/>
+      <c r="A102" s="16"/>
+      <c r="B102" s="19"/>
+      <c r="C102" s="22"/>
+      <c r="D102" s="26"/>
+      <c r="E102" s="26"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="26"/>
+      <c r="H102" s="26"/>
+      <c r="I102" s="27"/>
     </row>
     <row r="103" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="37"/>
-      <c r="B103" s="38"/>
-      <c r="C103" s="16"/>
-      <c r="D103" s="41"/>
-      <c r="E103" s="41"/>
-      <c r="F103" s="41"/>
-      <c r="G103" s="41"/>
-      <c r="H103" s="41"/>
-      <c r="I103" s="42"/>
+      <c r="A103" s="16"/>
+      <c r="B103" s="19"/>
+      <c r="C103" s="22"/>
+      <c r="D103" s="26"/>
+      <c r="E103" s="26"/>
+      <c r="F103" s="26"/>
+      <c r="G103" s="26"/>
+      <c r="H103" s="26"/>
+      <c r="I103" s="27"/>
     </row>
     <row r="104" spans="1:9" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="39"/>
-      <c r="B104" s="40"/>
-      <c r="C104" s="17"/>
-      <c r="D104" s="70"/>
-      <c r="E104" s="70"/>
-      <c r="F104" s="70"/>
-      <c r="G104" s="70"/>
-      <c r="H104" s="70"/>
-      <c r="I104" s="71"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
-      <c r="G105"/>
-      <c r="H105"/>
-      <c r="I105"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D106"/>
-      <c r="E106"/>
-      <c r="F106"/>
-      <c r="G106"/>
-      <c r="H106"/>
-      <c r="I106"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D107"/>
-      <c r="E107"/>
-      <c r="F107"/>
-      <c r="G107"/>
-      <c r="H107"/>
-      <c r="I107"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D108"/>
-      <c r="E108"/>
-      <c r="F108"/>
-      <c r="G108"/>
-      <c r="H108"/>
-      <c r="I108"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D109"/>
-      <c r="E109"/>
-      <c r="F109"/>
-      <c r="G109"/>
-      <c r="H109"/>
-      <c r="I109"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D110"/>
-      <c r="E110"/>
-      <c r="F110"/>
-      <c r="G110"/>
-      <c r="H110"/>
-      <c r="I110"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D111"/>
-      <c r="E111"/>
-      <c r="F111"/>
-      <c r="G111"/>
-      <c r="H111"/>
-      <c r="I111"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D112"/>
-      <c r="E112"/>
-      <c r="F112"/>
-      <c r="G112"/>
-      <c r="H112"/>
-      <c r="I112"/>
-    </row>
-    <row r="113" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="114" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="115" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="116" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="117" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="118" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="119" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="120" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="121" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="122" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="123" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="124" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="125" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="126" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="127" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="128" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="129" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="130" customFormat="1" x14ac:dyDescent="0.3"/>
+      <c r="A104" s="17"/>
+      <c r="B104" s="20"/>
+      <c r="C104" s="23"/>
+      <c r="D104" s="28"/>
+      <c r="E104" s="28"/>
+      <c r="F104" s="28"/>
+      <c r="G104" s="28"/>
+      <c r="H104" s="28"/>
+      <c r="I104" s="29"/>
+    </row>
+    <row r="105" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="12"/>
+      <c r="B105" s="13"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="13"/>
+      <c r="E105" s="13"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="13"/>
+      <c r="H105" s="13"/>
+      <c r="I105" s="14"/>
+    </row>
+    <row r="106" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="15"/>
+      <c r="B106" s="18"/>
+      <c r="C106" s="21"/>
+      <c r="D106" s="24"/>
+      <c r="E106" s="24"/>
+      <c r="F106" s="24"/>
+      <c r="G106" s="24"/>
+      <c r="H106" s="24"/>
+      <c r="I106" s="25"/>
+    </row>
+    <row r="107" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="16"/>
+      <c r="B107" s="19"/>
+      <c r="C107" s="22"/>
+      <c r="D107" s="26"/>
+      <c r="E107" s="26"/>
+      <c r="F107" s="26"/>
+      <c r="G107" s="26"/>
+      <c r="H107" s="26"/>
+      <c r="I107" s="27"/>
+    </row>
+    <row r="108" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="16"/>
+      <c r="B108" s="19"/>
+      <c r="C108" s="22"/>
+      <c r="D108" s="26"/>
+      <c r="E108" s="26"/>
+      <c r="F108" s="26"/>
+      <c r="G108" s="26"/>
+      <c r="H108" s="26"/>
+      <c r="I108" s="27"/>
+    </row>
+    <row r="109" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="16"/>
+      <c r="B109" s="19"/>
+      <c r="C109" s="22"/>
+      <c r="D109" s="26"/>
+      <c r="E109" s="26"/>
+      <c r="F109" s="26"/>
+      <c r="G109" s="26"/>
+      <c r="H109" s="26"/>
+      <c r="I109" s="27"/>
+    </row>
+    <row r="110" spans="1:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="16"/>
+      <c r="B110" s="19"/>
+      <c r="C110" s="22"/>
+      <c r="D110" s="26"/>
+      <c r="E110" s="26"/>
+      <c r="F110" s="26"/>
+      <c r="G110" s="26"/>
+      <c r="H110" s="26"/>
+      <c r="I110" s="27"/>
+    </row>
+    <row r="111" spans="1:9" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="17"/>
+      <c r="B111" s="20"/>
+      <c r="C111" s="23"/>
+      <c r="D111" s="28"/>
+      <c r="E111" s="28"/>
+      <c r="F111" s="28"/>
+      <c r="G111" s="28"/>
+      <c r="H111" s="28"/>
+      <c r="I111" s="29"/>
+    </row>
+    <row r="112" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="12"/>
+      <c r="B112" s="13"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="13"/>
+      <c r="E112" s="13"/>
+      <c r="F112" s="13"/>
+      <c r="G112" s="13"/>
+      <c r="H112" s="13"/>
+      <c r="I112" s="14"/>
+    </row>
+    <row r="113" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="15"/>
+      <c r="B113" s="18"/>
+      <c r="C113" s="21"/>
+      <c r="D113" s="24"/>
+      <c r="E113" s="24"/>
+      <c r="F113" s="24"/>
+      <c r="G113" s="24"/>
+      <c r="H113" s="24"/>
+      <c r="I113" s="25"/>
+    </row>
+    <row r="114" spans="1:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="16"/>
+      <c r="B114" s="19"/>
+      <c r="C114" s="22"/>
+      <c r="D114" s="26"/>
+      <c r="E114" s="26"/>
+      <c r="F114" s="26"/>
+      <c r="G114" s="26"/>
+      <c r="H114" s="26"/>
+      <c r="I114" s="27"/>
+    </row>
+    <row r="115" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="16"/>
+      <c r="B115" s="19"/>
+      <c r="C115" s="22"/>
+      <c r="D115" s="26"/>
+      <c r="E115" s="26"/>
+      <c r="F115" s="26"/>
+      <c r="G115" s="26"/>
+      <c r="H115" s="26"/>
+      <c r="I115" s="27"/>
+    </row>
+    <row r="116" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="16"/>
+      <c r="B116" s="19"/>
+      <c r="C116" s="22"/>
+      <c r="D116" s="26"/>
+      <c r="E116" s="26"/>
+      <c r="F116" s="26"/>
+      <c r="G116" s="26"/>
+      <c r="H116" s="26"/>
+      <c r="I116" s="27"/>
+    </row>
+    <row r="117" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="16"/>
+      <c r="B117" s="19"/>
+      <c r="C117" s="22"/>
+      <c r="D117" s="26"/>
+      <c r="E117" s="26"/>
+      <c r="F117" s="26"/>
+      <c r="G117" s="26"/>
+      <c r="H117" s="26"/>
+      <c r="I117" s="27"/>
+    </row>
+    <row r="118" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="17"/>
+      <c r="B118" s="20"/>
+      <c r="C118" s="23"/>
+      <c r="D118" s="28"/>
+      <c r="E118" s="28"/>
+      <c r="F118" s="28"/>
+      <c r="G118" s="28"/>
+      <c r="H118" s="28"/>
+      <c r="I118" s="29"/>
+    </row>
+    <row r="119" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="12"/>
+      <c r="B119" s="13"/>
+      <c r="C119" s="13"/>
+      <c r="D119" s="13"/>
+      <c r="E119" s="13"/>
+      <c r="F119" s="13"/>
+      <c r="G119" s="13"/>
+      <c r="H119" s="13"/>
+      <c r="I119" s="14"/>
+    </row>
+    <row r="120" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="15"/>
+      <c r="B120" s="18"/>
+      <c r="C120" s="21"/>
+      <c r="D120" s="24"/>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="24"/>
+      <c r="I120" s="25"/>
+    </row>
+    <row r="121" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="16"/>
+      <c r="B121" s="19"/>
+      <c r="C121" s="22"/>
+      <c r="D121" s="26"/>
+      <c r="E121" s="26"/>
+      <c r="F121" s="26"/>
+      <c r="G121" s="26"/>
+      <c r="H121" s="26"/>
+      <c r="I121" s="27"/>
+    </row>
+    <row r="122" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="16"/>
+      <c r="B122" s="19"/>
+      <c r="C122" s="22"/>
+      <c r="D122" s="26"/>
+      <c r="E122" s="26"/>
+      <c r="F122" s="26"/>
+      <c r="G122" s="26"/>
+      <c r="H122" s="26"/>
+      <c r="I122" s="27"/>
+    </row>
+    <row r="123" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="16"/>
+      <c r="B123" s="19"/>
+      <c r="C123" s="22"/>
+      <c r="D123" s="26"/>
+      <c r="E123" s="26"/>
+      <c r="F123" s="26"/>
+      <c r="G123" s="26"/>
+      <c r="H123" s="26"/>
+      <c r="I123" s="27"/>
+    </row>
+    <row r="124" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="16"/>
+      <c r="B124" s="19"/>
+      <c r="C124" s="22"/>
+      <c r="D124" s="26"/>
+      <c r="E124" s="26"/>
+      <c r="F124" s="26"/>
+      <c r="G124" s="26"/>
+      <c r="H124" s="26"/>
+      <c r="I124" s="27"/>
+    </row>
+    <row r="125" spans="1:9" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="17"/>
+      <c r="B125" s="20"/>
+      <c r="C125" s="23"/>
+      <c r="D125" s="28"/>
+      <c r="E125" s="28"/>
+      <c r="F125" s="28"/>
+      <c r="G125" s="28"/>
+      <c r="H125" s="28"/>
+      <c r="I125" s="29"/>
+    </row>
+    <row r="126" spans="1:9" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="12"/>
+      <c r="B126" s="13"/>
+      <c r="C126" s="13"/>
+      <c r="D126" s="13"/>
+      <c r="E126" s="13"/>
+      <c r="F126" s="13"/>
+      <c r="G126" s="13"/>
+      <c r="H126" s="13"/>
+      <c r="I126" s="14"/>
+    </row>
+    <row r="127" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="15"/>
+      <c r="B127" s="18"/>
+      <c r="C127" s="21"/>
+      <c r="D127" s="24"/>
+      <c r="E127" s="24"/>
+      <c r="F127" s="24"/>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="25"/>
+    </row>
+    <row r="128" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="16"/>
+      <c r="B128" s="19"/>
+      <c r="C128" s="22"/>
+      <c r="D128" s="26"/>
+      <c r="E128" s="26"/>
+      <c r="F128" s="26"/>
+      <c r="G128" s="26"/>
+      <c r="H128" s="26"/>
+      <c r="I128" s="27"/>
+    </row>
+    <row r="129" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="16"/>
+      <c r="B129" s="19"/>
+      <c r="C129" s="22"/>
+      <c r="D129" s="26"/>
+      <c r="E129" s="26"/>
+      <c r="F129" s="26"/>
+      <c r="G129" s="26"/>
+      <c r="H129" s="26"/>
+      <c r="I129" s="27"/>
+    </row>
+    <row r="130" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="16"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="22"/>
+      <c r="D130" s="26"/>
+      <c r="E130" s="26"/>
+      <c r="F130" s="26"/>
+      <c r="G130" s="26"/>
+      <c r="H130" s="26"/>
+      <c r="I130" s="27"/>
+    </row>
+    <row r="131" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="16"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="22"/>
+      <c r="D131" s="26"/>
+      <c r="E131" s="26"/>
+      <c r="F131" s="26"/>
+      <c r="G131" s="26"/>
+      <c r="H131" s="26"/>
+      <c r="I131" s="27"/>
+    </row>
+    <row r="132" spans="1:9" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="17"/>
+      <c r="B132" s="20"/>
+      <c r="C132" s="23"/>
+      <c r="D132" s="28"/>
+      <c r="E132" s="28"/>
+      <c r="F132" s="28"/>
+      <c r="G132" s="28"/>
+      <c r="H132" s="28"/>
+      <c r="I132" s="29"/>
+    </row>
+    <row r="133" spans="1:9" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="12"/>
+      <c r="B133" s="13"/>
+      <c r="C133" s="13"/>
+      <c r="D133" s="13"/>
+      <c r="E133" s="13"/>
+      <c r="F133" s="13"/>
+      <c r="G133" s="13"/>
+      <c r="H133" s="13"/>
+      <c r="I133" s="14"/>
+    </row>
+    <row r="134" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="15"/>
+      <c r="B134" s="18"/>
+      <c r="C134" s="21"/>
+      <c r="D134" s="24"/>
+      <c r="E134" s="24"/>
+      <c r="F134" s="24"/>
+      <c r="G134" s="24"/>
+      <c r="H134" s="24"/>
+      <c r="I134" s="25"/>
+    </row>
+    <row r="135" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="16"/>
+      <c r="B135" s="19"/>
+      <c r="C135" s="22"/>
+      <c r="D135" s="26"/>
+      <c r="E135" s="26"/>
+      <c r="F135" s="26"/>
+      <c r="G135" s="26"/>
+      <c r="H135" s="26"/>
+      <c r="I135" s="27"/>
+    </row>
+    <row r="136" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="16"/>
+      <c r="B136" s="19"/>
+      <c r="C136" s="22"/>
+      <c r="D136" s="26"/>
+      <c r="E136" s="26"/>
+      <c r="F136" s="26"/>
+      <c r="G136" s="26"/>
+      <c r="H136" s="26"/>
+      <c r="I136" s="27"/>
+    </row>
+    <row r="137" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="16"/>
+      <c r="B137" s="19"/>
+      <c r="C137" s="22"/>
+      <c r="D137" s="26"/>
+      <c r="E137" s="26"/>
+      <c r="F137" s="26"/>
+      <c r="G137" s="26"/>
+      <c r="H137" s="26"/>
+      <c r="I137" s="27"/>
+    </row>
+    <row r="138" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="16"/>
+      <c r="B138" s="19"/>
+      <c r="C138" s="22"/>
+      <c r="D138" s="26"/>
+      <c r="E138" s="26"/>
+      <c r="F138" s="26"/>
+      <c r="G138" s="26"/>
+      <c r="H138" s="26"/>
+      <c r="I138" s="27"/>
+    </row>
+    <row r="139" spans="1:9" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="17"/>
+      <c r="B139" s="20"/>
+      <c r="C139" s="23"/>
+      <c r="D139" s="28"/>
+      <c r="E139" s="28"/>
+      <c r="F139" s="28"/>
+      <c r="G139" s="28"/>
+      <c r="H139" s="28"/>
+      <c r="I139" s="29"/>
+    </row>
+    <row r="140" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="12"/>
+      <c r="B140" s="13"/>
+      <c r="C140" s="13"/>
+      <c r="D140" s="13"/>
+      <c r="E140" s="13"/>
+      <c r="F140" s="13"/>
+      <c r="G140" s="13"/>
+      <c r="H140" s="13"/>
+      <c r="I140" s="14"/>
+    </row>
+    <row r="141" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="15"/>
+      <c r="B141" s="18"/>
+      <c r="C141" s="21"/>
+      <c r="D141" s="24"/>
+      <c r="E141" s="24"/>
+      <c r="F141" s="24"/>
+      <c r="G141" s="24"/>
+      <c r="H141" s="24"/>
+      <c r="I141" s="25"/>
+    </row>
+    <row r="142" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="16"/>
+      <c r="B142" s="19"/>
+      <c r="C142" s="22"/>
+      <c r="D142" s="26"/>
+      <c r="E142" s="26"/>
+      <c r="F142" s="26"/>
+      <c r="G142" s="26"/>
+      <c r="H142" s="26"/>
+      <c r="I142" s="27"/>
+    </row>
+    <row r="143" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="16"/>
+      <c r="B143" s="19"/>
+      <c r="C143" s="22"/>
+      <c r="D143" s="26"/>
+      <c r="E143" s="26"/>
+      <c r="F143" s="26"/>
+      <c r="G143" s="26"/>
+      <c r="H143" s="26"/>
+      <c r="I143" s="27"/>
+    </row>
+    <row r="144" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="16"/>
+      <c r="B144" s="19"/>
+      <c r="C144" s="22"/>
+      <c r="D144" s="26"/>
+      <c r="E144" s="26"/>
+      <c r="F144" s="26"/>
+      <c r="G144" s="26"/>
+      <c r="H144" s="26"/>
+      <c r="I144" s="27"/>
+    </row>
+    <row r="145" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="16"/>
+      <c r="B145" s="19"/>
+      <c r="C145" s="22"/>
+      <c r="D145" s="26"/>
+      <c r="E145" s="26"/>
+      <c r="F145" s="26"/>
+      <c r="G145" s="26"/>
+      <c r="H145" s="26"/>
+      <c r="I145" s="27"/>
+    </row>
+    <row r="146" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="17"/>
+      <c r="B146" s="20"/>
+      <c r="C146" s="23"/>
+      <c r="D146" s="28"/>
+      <c r="E146" s="28"/>
+      <c r="F146" s="28"/>
+      <c r="G146" s="28"/>
+      <c r="H146" s="28"/>
+      <c r="I146" s="29"/>
+    </row>
+    <row r="147" spans="1:9" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="12"/>
+      <c r="B147" s="13"/>
+      <c r="C147" s="13"/>
+      <c r="D147" s="13"/>
+      <c r="E147" s="13"/>
+      <c r="F147" s="13"/>
+      <c r="G147" s="13"/>
+      <c r="H147" s="13"/>
+      <c r="I147" s="14"/>
+    </row>
+    <row r="148" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="15"/>
+      <c r="B148" s="18"/>
+      <c r="C148" s="21"/>
+      <c r="D148" s="24"/>
+      <c r="E148" s="24"/>
+      <c r="F148" s="24"/>
+      <c r="G148" s="24"/>
+      <c r="H148" s="24"/>
+      <c r="I148" s="25"/>
+    </row>
+    <row r="149" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="16"/>
+      <c r="B149" s="19"/>
+      <c r="C149" s="22"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="26"/>
+      <c r="F149" s="26"/>
+      <c r="G149" s="26"/>
+      <c r="H149" s="26"/>
+      <c r="I149" s="27"/>
+    </row>
+    <row r="150" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="16"/>
+      <c r="B150" s="19"/>
+      <c r="C150" s="22"/>
+      <c r="D150" s="26"/>
+      <c r="E150" s="26"/>
+      <c r="F150" s="26"/>
+      <c r="G150" s="26"/>
+      <c r="H150" s="26"/>
+      <c r="I150" s="27"/>
+    </row>
+    <row r="151" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="16"/>
+      <c r="B151" s="19"/>
+      <c r="C151" s="22"/>
+      <c r="D151" s="26"/>
+      <c r="E151" s="26"/>
+      <c r="F151" s="26"/>
+      <c r="G151" s="26"/>
+      <c r="H151" s="26"/>
+      <c r="I151" s="27"/>
+    </row>
+    <row r="152" spans="1:9" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="16"/>
+      <c r="B152" s="19"/>
+      <c r="C152" s="22"/>
+      <c r="D152" s="26"/>
+      <c r="E152" s="26"/>
+      <c r="F152" s="26"/>
+      <c r="G152" s="26"/>
+      <c r="H152" s="26"/>
+      <c r="I152" s="27"/>
+    </row>
+    <row r="153" spans="1:9" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="17"/>
+      <c r="B153" s="20"/>
+      <c r="C153" s="23"/>
+      <c r="D153" s="28"/>
+      <c r="E153" s="28"/>
+      <c r="F153" s="28"/>
+      <c r="G153" s="28"/>
+      <c r="H153" s="28"/>
+      <c r="I153" s="29"/>
+    </row>
+    <row r="154" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="12"/>
+      <c r="B154" s="13"/>
+      <c r="C154" s="13"/>
+      <c r="D154" s="13"/>
+      <c r="E154" s="13"/>
+      <c r="F154" s="13"/>
+      <c r="G154" s="13"/>
+      <c r="H154" s="13"/>
+      <c r="I154" s="14"/>
+    </row>
+    <row r="155" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="15"/>
+      <c r="B155" s="18"/>
+      <c r="C155" s="21"/>
+      <c r="D155" s="24"/>
+      <c r="E155" s="24"/>
+      <c r="F155" s="24"/>
+      <c r="G155" s="24"/>
+      <c r="H155" s="24"/>
+      <c r="I155" s="25"/>
+    </row>
+    <row r="156" spans="1:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="16"/>
+      <c r="B156" s="19"/>
+      <c r="C156" s="22"/>
+      <c r="D156" s="26"/>
+      <c r="E156" s="26"/>
+      <c r="F156" s="26"/>
+      <c r="G156" s="26"/>
+      <c r="H156" s="26"/>
+      <c r="I156" s="27"/>
+    </row>
+    <row r="157" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="16"/>
+      <c r="B157" s="19"/>
+      <c r="C157" s="22"/>
+      <c r="D157" s="26"/>
+      <c r="E157" s="26"/>
+      <c r="F157" s="26"/>
+      <c r="G157" s="26"/>
+      <c r="H157" s="26"/>
+      <c r="I157" s="27"/>
+    </row>
+    <row r="158" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="16"/>
+      <c r="B158" s="19"/>
+      <c r="C158" s="22"/>
+      <c r="D158" s="26"/>
+      <c r="E158" s="26"/>
+      <c r="F158" s="26"/>
+      <c r="G158" s="26"/>
+      <c r="H158" s="26"/>
+      <c r="I158" s="27"/>
+    </row>
+    <row r="159" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="16"/>
+      <c r="B159" s="19"/>
+      <c r="C159" s="22"/>
+      <c r="D159" s="26"/>
+      <c r="E159" s="26"/>
+      <c r="F159" s="26"/>
+      <c r="G159" s="26"/>
+      <c r="H159" s="26"/>
+      <c r="I159" s="27"/>
+    </row>
+    <row r="160" spans="1:9" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="17"/>
+      <c r="B160" s="20"/>
+      <c r="C160" s="23"/>
+      <c r="D160" s="28"/>
+      <c r="E160" s="28"/>
+      <c r="F160" s="28"/>
+      <c r="G160" s="28"/>
+      <c r="H160" s="28"/>
+      <c r="I160" s="29"/>
+    </row>
+    <row r="161" spans="1:9" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="12"/>
+      <c r="B161" s="13"/>
+      <c r="C161" s="13"/>
+      <c r="D161" s="13"/>
+      <c r="E161" s="13"/>
+      <c r="F161" s="13"/>
+      <c r="G161" s="13"/>
+      <c r="H161" s="13"/>
+      <c r="I161" s="14"/>
+    </row>
+    <row r="162" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="15"/>
+      <c r="B162" s="18"/>
+      <c r="C162" s="21"/>
+      <c r="D162" s="24"/>
+      <c r="E162" s="24"/>
+      <c r="F162" s="24"/>
+      <c r="G162" s="24"/>
+      <c r="H162" s="24"/>
+      <c r="I162" s="25"/>
+    </row>
+    <row r="163" spans="1:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="16"/>
+      <c r="B163" s="19"/>
+      <c r="C163" s="22"/>
+      <c r="D163" s="26"/>
+      <c r="E163" s="26"/>
+      <c r="F163" s="26"/>
+      <c r="G163" s="26"/>
+      <c r="H163" s="26"/>
+      <c r="I163" s="27"/>
+    </row>
+    <row r="164" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="16"/>
+      <c r="B164" s="19"/>
+      <c r="C164" s="22"/>
+      <c r="D164" s="26"/>
+      <c r="E164" s="26"/>
+      <c r="F164" s="26"/>
+      <c r="G164" s="26"/>
+      <c r="H164" s="26"/>
+      <c r="I164" s="27"/>
+    </row>
+    <row r="165" spans="1:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="16"/>
+      <c r="B165" s="19"/>
+      <c r="C165" s="22"/>
+      <c r="D165" s="26"/>
+      <c r="E165" s="26"/>
+      <c r="F165" s="26"/>
+      <c r="G165" s="26"/>
+      <c r="H165" s="26"/>
+      <c r="I165" s="27"/>
+    </row>
+    <row r="166" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="16"/>
+      <c r="B166" s="19"/>
+      <c r="C166" s="22"/>
+      <c r="D166" s="26"/>
+      <c r="E166" s="26"/>
+      <c r="F166" s="26"/>
+      <c r="G166" s="26"/>
+      <c r="H166" s="26"/>
+      <c r="I166" s="27"/>
+    </row>
+    <row r="167" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="17"/>
+      <c r="B167" s="20"/>
+      <c r="C167" s="23"/>
+      <c r="D167" s="28"/>
+      <c r="E167" s="28"/>
+      <c r="F167" s="28"/>
+      <c r="G167" s="28"/>
+      <c r="H167" s="28"/>
+      <c r="I167" s="29"/>
+    </row>
+    <row r="168" spans="1:9" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="12"/>
+      <c r="B168" s="13"/>
+      <c r="C168" s="13"/>
+      <c r="D168" s="13"/>
+      <c r="E168" s="13"/>
+      <c r="F168" s="13"/>
+      <c r="G168" s="13"/>
+      <c r="H168" s="13"/>
+      <c r="I168" s="14"/>
+    </row>
+    <row r="169" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="15"/>
+      <c r="B169" s="18"/>
+      <c r="C169" s="21"/>
+      <c r="D169" s="24"/>
+      <c r="E169" s="24"/>
+      <c r="F169" s="24"/>
+      <c r="G169" s="24"/>
+      <c r="H169" s="24"/>
+      <c r="I169" s="25"/>
+    </row>
+    <row r="170" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="16"/>
+      <c r="B170" s="19"/>
+      <c r="C170" s="22"/>
+      <c r="D170" s="26"/>
+      <c r="E170" s="26"/>
+      <c r="F170" s="26"/>
+      <c r="G170" s="26"/>
+      <c r="H170" s="26"/>
+      <c r="I170" s="27"/>
+    </row>
+    <row r="171" spans="1:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="16"/>
+      <c r="B171" s="19"/>
+      <c r="C171" s="22"/>
+      <c r="D171" s="26"/>
+      <c r="E171" s="26"/>
+      <c r="F171" s="26"/>
+      <c r="G171" s="26"/>
+      <c r="H171" s="26"/>
+      <c r="I171" s="27"/>
+    </row>
+    <row r="172" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="16"/>
+      <c r="B172" s="19"/>
+      <c r="C172" s="22"/>
+      <c r="D172" s="26"/>
+      <c r="E172" s="26"/>
+      <c r="F172" s="26"/>
+      <c r="G172" s="26"/>
+      <c r="H172" s="26"/>
+      <c r="I172" s="27"/>
+    </row>
+    <row r="173" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="16"/>
+      <c r="B173" s="19"/>
+      <c r="C173" s="22"/>
+      <c r="D173" s="26"/>
+      <c r="E173" s="26"/>
+      <c r="F173" s="26"/>
+      <c r="G173" s="26"/>
+      <c r="H173" s="26"/>
+      <c r="I173" s="27"/>
+    </row>
+    <row r="174" spans="1:9" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="17"/>
+      <c r="B174" s="20"/>
+      <c r="C174" s="23"/>
+      <c r="D174" s="28"/>
+      <c r="E174" s="28"/>
+      <c r="F174" s="28"/>
+      <c r="G174" s="28"/>
+      <c r="H174" s="28"/>
+      <c r="I174" s="29"/>
+    </row>
+    <row r="175" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="12"/>
+      <c r="B175" s="13"/>
+      <c r="C175" s="13"/>
+      <c r="D175" s="13"/>
+      <c r="E175" s="13"/>
+      <c r="F175" s="13"/>
+      <c r="G175" s="13"/>
+      <c r="H175" s="13"/>
+      <c r="I175" s="14"/>
+    </row>
+    <row r="176" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="15"/>
+      <c r="B176" s="18"/>
+      <c r="C176" s="21"/>
+      <c r="D176" s="24"/>
+      <c r="E176" s="24"/>
+      <c r="F176" s="24"/>
+      <c r="G176" s="24"/>
+      <c r="H176" s="24"/>
+      <c r="I176" s="25"/>
+    </row>
+    <row r="177" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="16"/>
+      <c r="B177" s="19"/>
+      <c r="C177" s="22"/>
+      <c r="D177" s="26"/>
+      <c r="E177" s="26"/>
+      <c r="F177" s="26"/>
+      <c r="G177" s="26"/>
+      <c r="H177" s="26"/>
+      <c r="I177" s="27"/>
+    </row>
+    <row r="178" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="16"/>
+      <c r="B178" s="19"/>
+      <c r="C178" s="22"/>
+      <c r="D178" s="26"/>
+      <c r="E178" s="26"/>
+      <c r="F178" s="26"/>
+      <c r="G178" s="26"/>
+      <c r="H178" s="26"/>
+      <c r="I178" s="27"/>
+    </row>
+    <row r="179" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="16"/>
+      <c r="B179" s="19"/>
+      <c r="C179" s="22"/>
+      <c r="D179" s="26"/>
+      <c r="E179" s="26"/>
+      <c r="F179" s="26"/>
+      <c r="G179" s="26"/>
+      <c r="H179" s="26"/>
+      <c r="I179" s="27"/>
+    </row>
+    <row r="180" spans="1:9" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="16"/>
+      <c r="B180" s="19"/>
+      <c r="C180" s="22"/>
+      <c r="D180" s="26"/>
+      <c r="E180" s="26"/>
+      <c r="F180" s="26"/>
+      <c r="G180" s="26"/>
+      <c r="H180" s="26"/>
+      <c r="I180" s="27"/>
+    </row>
+    <row r="181" spans="1:9" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="17"/>
+      <c r="B181" s="20"/>
+      <c r="C181" s="23"/>
+      <c r="D181" s="28"/>
+      <c r="E181" s="28"/>
+      <c r="F181" s="28"/>
+      <c r="G181" s="28"/>
+      <c r="H181" s="28"/>
+      <c r="I181" s="29"/>
+    </row>
+    <row r="182" spans="1:9" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="12"/>
+      <c r="B182" s="13"/>
+      <c r="C182" s="13"/>
+      <c r="D182" s="13"/>
+      <c r="E182" s="13"/>
+      <c r="F182" s="13"/>
+      <c r="G182" s="13"/>
+      <c r="H182" s="13"/>
+      <c r="I182" s="14"/>
+    </row>
+    <row r="183" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="15"/>
+      <c r="B183" s="18"/>
+      <c r="C183" s="21"/>
+      <c r="D183" s="24"/>
+      <c r="E183" s="24"/>
+      <c r="F183" s="24"/>
+      <c r="G183" s="24"/>
+      <c r="H183" s="24"/>
+      <c r="I183" s="25"/>
+    </row>
+    <row r="184" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="16"/>
+      <c r="B184" s="19"/>
+      <c r="C184" s="22"/>
+      <c r="D184" s="26"/>
+      <c r="E184" s="26"/>
+      <c r="F184" s="26"/>
+      <c r="G184" s="26"/>
+      <c r="H184" s="26"/>
+      <c r="I184" s="27"/>
+    </row>
+    <row r="185" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="16"/>
+      <c r="B185" s="19"/>
+      <c r="C185" s="22"/>
+      <c r="D185" s="26"/>
+      <c r="E185" s="26"/>
+      <c r="F185" s="26"/>
+      <c r="G185" s="26"/>
+      <c r="H185" s="26"/>
+      <c r="I185" s="27"/>
+    </row>
+    <row r="186" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="16"/>
+      <c r="B186" s="19"/>
+      <c r="C186" s="22"/>
+      <c r="D186" s="26"/>
+      <c r="E186" s="26"/>
+      <c r="F186" s="26"/>
+      <c r="G186" s="26"/>
+      <c r="H186" s="26"/>
+      <c r="I186" s="27"/>
+    </row>
+    <row r="187" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="16"/>
+      <c r="B187" s="19"/>
+      <c r="C187" s="22"/>
+      <c r="D187" s="26"/>
+      <c r="E187" s="26"/>
+      <c r="F187" s="26"/>
+      <c r="G187" s="26"/>
+      <c r="H187" s="26"/>
+      <c r="I187" s="27"/>
+    </row>
+    <row r="188" spans="1:9" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A188" s="17"/>
+      <c r="B188" s="20"/>
+      <c r="C188" s="23"/>
+      <c r="D188" s="28"/>
+      <c r="E188" s="28"/>
+      <c r="F188" s="28"/>
+      <c r="G188" s="28"/>
+      <c r="H188" s="28"/>
+      <c r="I188" s="29"/>
+    </row>
+    <row r="189" spans="1:9" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A189" s="12"/>
+      <c r="B189" s="13"/>
+      <c r="C189" s="13"/>
+      <c r="D189" s="13"/>
+      <c r="E189" s="13"/>
+      <c r="F189" s="13"/>
+      <c r="G189" s="13"/>
+      <c r="H189" s="13"/>
+      <c r="I189" s="14"/>
+    </row>
+    <row r="190" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="15"/>
+      <c r="B190" s="18"/>
+      <c r="C190" s="21"/>
+      <c r="D190" s="24"/>
+      <c r="E190" s="24"/>
+      <c r="F190" s="24"/>
+      <c r="G190" s="24"/>
+      <c r="H190" s="24"/>
+      <c r="I190" s="25"/>
+    </row>
+    <row r="191" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="16"/>
+      <c r="B191" s="19"/>
+      <c r="C191" s="22"/>
+      <c r="D191" s="26"/>
+      <c r="E191" s="26"/>
+      <c r="F191" s="26"/>
+      <c r="G191" s="26"/>
+      <c r="H191" s="26"/>
+      <c r="I191" s="27"/>
+    </row>
+    <row r="192" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="16"/>
+      <c r="B192" s="19"/>
+      <c r="C192" s="22"/>
+      <c r="D192" s="26"/>
+      <c r="E192" s="26"/>
+      <c r="F192" s="26"/>
+      <c r="G192" s="26"/>
+      <c r="H192" s="26"/>
+      <c r="I192" s="27"/>
+    </row>
+    <row r="193" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="16"/>
+      <c r="B193" s="19"/>
+      <c r="C193" s="22"/>
+      <c r="D193" s="26"/>
+      <c r="E193" s="26"/>
+      <c r="F193" s="26"/>
+      <c r="G193" s="26"/>
+      <c r="H193" s="26"/>
+      <c r="I193" s="27"/>
+    </row>
+    <row r="194" spans="1:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="16"/>
+      <c r="B194" s="19"/>
+      <c r="C194" s="22"/>
+      <c r="D194" s="26"/>
+      <c r="E194" s="26"/>
+      <c r="F194" s="26"/>
+      <c r="G194" s="26"/>
+      <c r="H194" s="26"/>
+      <c r="I194" s="27"/>
+    </row>
+    <row r="195" spans="1:9" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A195" s="17"/>
+      <c r="B195" s="20"/>
+      <c r="C195" s="23"/>
+      <c r="D195" s="28"/>
+      <c r="E195" s="28"/>
+      <c r="F195" s="28"/>
+      <c r="G195" s="28"/>
+      <c r="H195" s="28"/>
+      <c r="I195" s="29"/>
+    </row>
+    <row r="196" spans="1:9" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A196" s="12"/>
+      <c r="B196" s="13"/>
+      <c r="C196" s="13"/>
+      <c r="D196" s="13"/>
+      <c r="E196" s="13"/>
+      <c r="F196" s="13"/>
+      <c r="G196" s="13"/>
+      <c r="H196" s="13"/>
+      <c r="I196" s="14"/>
+    </row>
+    <row r="197" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="15"/>
+      <c r="B197" s="18"/>
+      <c r="C197" s="21"/>
+      <c r="D197" s="24"/>
+      <c r="E197" s="24"/>
+      <c r="F197" s="24"/>
+      <c r="G197" s="24"/>
+      <c r="H197" s="24"/>
+      <c r="I197" s="25"/>
+    </row>
+    <row r="198" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="16"/>
+      <c r="B198" s="19"/>
+      <c r="C198" s="22"/>
+      <c r="D198" s="26"/>
+      <c r="E198" s="26"/>
+      <c r="F198" s="26"/>
+      <c r="G198" s="26"/>
+      <c r="H198" s="26"/>
+      <c r="I198" s="27"/>
+    </row>
+    <row r="199" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="16"/>
+      <c r="B199" s="19"/>
+      <c r="C199" s="22"/>
+      <c r="D199" s="26"/>
+      <c r="E199" s="26"/>
+      <c r="F199" s="26"/>
+      <c r="G199" s="26"/>
+      <c r="H199" s="26"/>
+      <c r="I199" s="27"/>
+    </row>
+    <row r="200" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="16"/>
+      <c r="B200" s="19"/>
+      <c r="C200" s="22"/>
+      <c r="D200" s="26"/>
+      <c r="E200" s="26"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="26"/>
+      <c r="H200" s="26"/>
+      <c r="I200" s="27"/>
+    </row>
+    <row r="201" spans="1:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="16"/>
+      <c r="B201" s="19"/>
+      <c r="C201" s="22"/>
+      <c r="D201" s="26"/>
+      <c r="E201" s="26"/>
+      <c r="F201" s="26"/>
+      <c r="G201" s="26"/>
+      <c r="H201" s="26"/>
+      <c r="I201" s="27"/>
+    </row>
+    <row r="202" spans="1:9" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A202" s="17"/>
+      <c r="B202" s="20"/>
+      <c r="C202" s="23"/>
+      <c r="D202" s="28"/>
+      <c r="E202" s="28"/>
+      <c r="F202" s="28"/>
+      <c r="G202" s="28"/>
+      <c r="H202" s="28"/>
+      <c r="I202" s="29"/>
+    </row>
+    <row r="203" spans="1:9" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A203" s="12"/>
+      <c r="B203" s="13"/>
+      <c r="C203" s="13"/>
+      <c r="D203" s="13"/>
+      <c r="E203" s="13"/>
+      <c r="F203" s="13"/>
+      <c r="G203" s="13"/>
+      <c r="H203" s="13"/>
+      <c r="I203" s="14"/>
+    </row>
+    <row r="204" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="15"/>
+      <c r="B204" s="18"/>
+      <c r="C204" s="21"/>
+      <c r="D204" s="24"/>
+      <c r="E204" s="24"/>
+      <c r="F204" s="24"/>
+      <c r="G204" s="24"/>
+      <c r="H204" s="24"/>
+      <c r="I204" s="25"/>
+    </row>
+    <row r="205" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="16"/>
+      <c r="B205" s="19"/>
+      <c r="C205" s="22"/>
+      <c r="D205" s="26"/>
+      <c r="E205" s="26"/>
+      <c r="F205" s="26"/>
+      <c r="G205" s="26"/>
+      <c r="H205" s="26"/>
+      <c r="I205" s="27"/>
+    </row>
+    <row r="206" spans="1:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="16"/>
+      <c r="B206" s="19"/>
+      <c r="C206" s="22"/>
+      <c r="D206" s="26"/>
+      <c r="E206" s="26"/>
+      <c r="F206" s="26"/>
+      <c r="G206" s="26"/>
+      <c r="H206" s="26"/>
+      <c r="I206" s="27"/>
+    </row>
+    <row r="207" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="16"/>
+      <c r="B207" s="19"/>
+      <c r="C207" s="22"/>
+      <c r="D207" s="26"/>
+      <c r="E207" s="26"/>
+      <c r="F207" s="26"/>
+      <c r="G207" s="26"/>
+      <c r="H207" s="26"/>
+      <c r="I207" s="27"/>
+    </row>
+    <row r="208" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="16"/>
+      <c r="B208" s="19"/>
+      <c r="C208" s="22"/>
+      <c r="D208" s="26"/>
+      <c r="E208" s="26"/>
+      <c r="F208" s="26"/>
+      <c r="G208" s="26"/>
+      <c r="H208" s="26"/>
+      <c r="I208" s="27"/>
+    </row>
+    <row r="209" spans="1:9" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A209" s="17"/>
+      <c r="B209" s="20"/>
+      <c r="C209" s="23"/>
+      <c r="D209" s="28"/>
+      <c r="E209" s="28"/>
+      <c r="F209" s="28"/>
+      <c r="G209" s="28"/>
+      <c r="H209" s="28"/>
+      <c r="I209" s="29"/>
+    </row>
+    <row r="210" spans="1:9" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A210" s="12"/>
+      <c r="B210" s="13"/>
+      <c r="C210" s="13"/>
+      <c r="D210" s="13"/>
+      <c r="E210" s="13"/>
+      <c r="F210" s="13"/>
+      <c r="G210" s="13"/>
+      <c r="H210" s="13"/>
+      <c r="I210" s="14"/>
+    </row>
+    <row r="211" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="15"/>
+      <c r="B211" s="18"/>
+      <c r="C211" s="21"/>
+      <c r="D211" s="24"/>
+      <c r="E211" s="24"/>
+      <c r="F211" s="24"/>
+      <c r="G211" s="24"/>
+      <c r="H211" s="24"/>
+      <c r="I211" s="25"/>
+    </row>
+    <row r="212" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="16"/>
+      <c r="B212" s="19"/>
+      <c r="C212" s="22"/>
+      <c r="D212" s="26"/>
+      <c r="E212" s="26"/>
+      <c r="F212" s="26"/>
+      <c r="G212" s="26"/>
+      <c r="H212" s="26"/>
+      <c r="I212" s="27"/>
+    </row>
+    <row r="213" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="16"/>
+      <c r="B213" s="19"/>
+      <c r="C213" s="22"/>
+      <c r="D213" s="26"/>
+      <c r="E213" s="26"/>
+      <c r="F213" s="26"/>
+      <c r="G213" s="26"/>
+      <c r="H213" s="26"/>
+      <c r="I213" s="27"/>
+    </row>
+    <row r="214" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="16"/>
+      <c r="B214" s="19"/>
+      <c r="C214" s="22"/>
+      <c r="D214" s="26"/>
+      <c r="E214" s="26"/>
+      <c r="F214" s="26"/>
+      <c r="G214" s="26"/>
+      <c r="H214" s="26"/>
+      <c r="I214" s="27"/>
+    </row>
+    <row r="215" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="16"/>
+      <c r="B215" s="19"/>
+      <c r="C215" s="22"/>
+      <c r="D215" s="26"/>
+      <c r="E215" s="26"/>
+      <c r="F215" s="26"/>
+      <c r="G215" s="26"/>
+      <c r="H215" s="26"/>
+      <c r="I215" s="27"/>
+    </row>
+    <row r="216" spans="1:9" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A216" s="17"/>
+      <c r="B216" s="20"/>
+      <c r="C216" s="23"/>
+      <c r="D216" s="28"/>
+      <c r="E216" s="28"/>
+      <c r="F216" s="28"/>
+      <c r="G216" s="28"/>
+      <c r="H216" s="28"/>
+      <c r="I216" s="29"/>
+    </row>
+    <row r="217" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A217" s="12"/>
+      <c r="B217" s="13"/>
+      <c r="C217" s="13"/>
+      <c r="D217" s="13"/>
+      <c r="E217" s="13"/>
+      <c r="F217" s="13"/>
+      <c r="G217" s="13"/>
+      <c r="H217" s="13"/>
+      <c r="I217" s="14"/>
+    </row>
+    <row r="218" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="15"/>
+      <c r="B218" s="18"/>
+      <c r="C218" s="21"/>
+      <c r="D218" s="24"/>
+      <c r="E218" s="24"/>
+      <c r="F218" s="24"/>
+      <c r="G218" s="24"/>
+      <c r="H218" s="24"/>
+      <c r="I218" s="25"/>
+    </row>
+    <row r="219" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="16"/>
+      <c r="B219" s="19"/>
+      <c r="C219" s="22"/>
+      <c r="D219" s="26"/>
+      <c r="E219" s="26"/>
+      <c r="F219" s="26"/>
+      <c r="G219" s="26"/>
+      <c r="H219" s="26"/>
+      <c r="I219" s="27"/>
+    </row>
+    <row r="220" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="16"/>
+      <c r="B220" s="19"/>
+      <c r="C220" s="22"/>
+      <c r="D220" s="26"/>
+      <c r="E220" s="26"/>
+      <c r="F220" s="26"/>
+      <c r="G220" s="26"/>
+      <c r="H220" s="26"/>
+      <c r="I220" s="27"/>
+    </row>
+    <row r="221" spans="1:9" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="16"/>
+      <c r="B221" s="19"/>
+      <c r="C221" s="22"/>
+      <c r="D221" s="26"/>
+      <c r="E221" s="26"/>
+      <c r="F221" s="26"/>
+      <c r="G221" s="26"/>
+      <c r="H221" s="26"/>
+      <c r="I221" s="27"/>
+    </row>
+    <row r="222" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="16"/>
+      <c r="B222" s="19"/>
+      <c r="C222" s="22"/>
+      <c r="D222" s="26"/>
+      <c r="E222" s="26"/>
+      <c r="F222" s="26"/>
+      <c r="G222" s="26"/>
+      <c r="H222" s="26"/>
+      <c r="I222" s="27"/>
+    </row>
+    <row r="223" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A223" s="17"/>
+      <c r="B223" s="20"/>
+      <c r="C223" s="23"/>
+      <c r="D223" s="28"/>
+      <c r="E223" s="28"/>
+      <c r="F223" s="28"/>
+      <c r="G223" s="28"/>
+      <c r="H223" s="28"/>
+      <c r="I223" s="29"/>
+    </row>
+    <row r="224" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A224" s="12"/>
+      <c r="B224" s="13"/>
+      <c r="C224" s="13"/>
+      <c r="D224" s="13"/>
+      <c r="E224" s="13"/>
+      <c r="F224" s="13"/>
+      <c r="G224" s="13"/>
+      <c r="H224" s="13"/>
+      <c r="I224" s="14"/>
+    </row>
+    <row r="225" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="15"/>
+      <c r="B225" s="18"/>
+      <c r="C225" s="21"/>
+      <c r="D225" s="24"/>
+      <c r="E225" s="24"/>
+      <c r="F225" s="24"/>
+      <c r="G225" s="24"/>
+      <c r="H225" s="24"/>
+      <c r="I225" s="25"/>
+    </row>
+    <row r="226" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="16"/>
+      <c r="B226" s="19"/>
+      <c r="C226" s="22"/>
+      <c r="D226" s="26"/>
+      <c r="E226" s="26"/>
+      <c r="F226" s="26"/>
+      <c r="G226" s="26"/>
+      <c r="H226" s="26"/>
+      <c r="I226" s="27"/>
+    </row>
+    <row r="227" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="16"/>
+      <c r="B227" s="19"/>
+      <c r="C227" s="22"/>
+      <c r="D227" s="26"/>
+      <c r="E227" s="26"/>
+      <c r="F227" s="26"/>
+      <c r="G227" s="26"/>
+      <c r="H227" s="26"/>
+      <c r="I227" s="27"/>
+    </row>
+    <row r="228" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="16"/>
+      <c r="B228" s="19"/>
+      <c r="C228" s="22"/>
+      <c r="D228" s="26"/>
+      <c r="E228" s="26"/>
+      <c r="F228" s="26"/>
+      <c r="G228" s="26"/>
+      <c r="H228" s="26"/>
+      <c r="I228" s="27"/>
+    </row>
+    <row r="229" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="16"/>
+      <c r="B229" s="19"/>
+      <c r="C229" s="22"/>
+      <c r="D229" s="26"/>
+      <c r="E229" s="26"/>
+      <c r="F229" s="26"/>
+      <c r="G229" s="26"/>
+      <c r="H229" s="26"/>
+      <c r="I229" s="27"/>
+    </row>
+    <row r="230" spans="1:9" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A230" s="17"/>
+      <c r="B230" s="20"/>
+      <c r="C230" s="23"/>
+      <c r="D230" s="28"/>
+      <c r="E230" s="28"/>
+      <c r="F230" s="28"/>
+      <c r="G230" s="28"/>
+      <c r="H230" s="28"/>
+      <c r="I230" s="29"/>
+    </row>
   </sheetData>
-  <mergeCells count="75">
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A71:A76"/>
-    <mergeCell ref="B71:B76"/>
-    <mergeCell ref="C71:C76"/>
-    <mergeCell ref="D71:I76"/>
-    <mergeCell ref="A29:A34"/>
-    <mergeCell ref="B29:B34"/>
-    <mergeCell ref="C29:C34"/>
-    <mergeCell ref="D29:I34"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="D36:I41"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="B43:B48"/>
-    <mergeCell ref="C43:C48"/>
-    <mergeCell ref="D43:I48"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A84:I84"/>
-    <mergeCell ref="A85:A90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C85:C90"/>
-    <mergeCell ref="D85:I90"/>
-    <mergeCell ref="A77:I77"/>
-    <mergeCell ref="A78:A83"/>
-    <mergeCell ref="B78:B83"/>
-    <mergeCell ref="C78:C83"/>
-    <mergeCell ref="D78:I83"/>
-    <mergeCell ref="A63:I63"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="B64:B69"/>
-    <mergeCell ref="A50:A55"/>
-    <mergeCell ref="B50:B55"/>
-    <mergeCell ref="C50:C55"/>
-    <mergeCell ref="D50:I55"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="A57:A62"/>
-    <mergeCell ref="B57:B62"/>
-    <mergeCell ref="C57:C62"/>
-    <mergeCell ref="D57:I62"/>
-    <mergeCell ref="C64:C69"/>
-    <mergeCell ref="D64:I69"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="D22:I27"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="D10:I13"/>
+  <mergeCells count="165">
+    <mergeCell ref="A224:I224"/>
+    <mergeCell ref="A225:A230"/>
+    <mergeCell ref="B225:B230"/>
+    <mergeCell ref="C225:C230"/>
+    <mergeCell ref="D225:I230"/>
+    <mergeCell ref="A217:I217"/>
+    <mergeCell ref="A218:A223"/>
+    <mergeCell ref="B218:B223"/>
+    <mergeCell ref="C218:C223"/>
+    <mergeCell ref="D218:I223"/>
+    <mergeCell ref="A210:I210"/>
+    <mergeCell ref="A211:A216"/>
+    <mergeCell ref="B211:B216"/>
+    <mergeCell ref="C211:C216"/>
+    <mergeCell ref="D211:I216"/>
+    <mergeCell ref="A203:I203"/>
+    <mergeCell ref="A204:A209"/>
+    <mergeCell ref="B204:B209"/>
+    <mergeCell ref="C204:C209"/>
+    <mergeCell ref="D204:I209"/>
+    <mergeCell ref="A196:I196"/>
+    <mergeCell ref="A197:A202"/>
+    <mergeCell ref="B197:B202"/>
+    <mergeCell ref="C197:C202"/>
+    <mergeCell ref="D197:I202"/>
+    <mergeCell ref="A189:I189"/>
+    <mergeCell ref="A190:A195"/>
+    <mergeCell ref="B190:B195"/>
+    <mergeCell ref="C190:C195"/>
+    <mergeCell ref="D190:I195"/>
+    <mergeCell ref="A182:I182"/>
+    <mergeCell ref="A183:A188"/>
+    <mergeCell ref="B183:B188"/>
+    <mergeCell ref="C183:C188"/>
+    <mergeCell ref="D183:I188"/>
+    <mergeCell ref="A175:I175"/>
+    <mergeCell ref="A176:A181"/>
+    <mergeCell ref="B176:B181"/>
+    <mergeCell ref="C176:C181"/>
+    <mergeCell ref="D176:I181"/>
+    <mergeCell ref="A168:I168"/>
+    <mergeCell ref="A169:A174"/>
+    <mergeCell ref="B169:B174"/>
+    <mergeCell ref="C169:C174"/>
+    <mergeCell ref="D169:I174"/>
+    <mergeCell ref="A161:I161"/>
+    <mergeCell ref="A162:A167"/>
+    <mergeCell ref="B162:B167"/>
+    <mergeCell ref="C162:C167"/>
+    <mergeCell ref="D162:I167"/>
+    <mergeCell ref="A154:I154"/>
+    <mergeCell ref="A155:A160"/>
+    <mergeCell ref="B155:B160"/>
+    <mergeCell ref="C155:C160"/>
+    <mergeCell ref="D155:I160"/>
+    <mergeCell ref="A147:I147"/>
+    <mergeCell ref="A148:A153"/>
+    <mergeCell ref="B148:B153"/>
+    <mergeCell ref="C148:C153"/>
+    <mergeCell ref="D148:I153"/>
+    <mergeCell ref="A140:I140"/>
+    <mergeCell ref="A141:A146"/>
+    <mergeCell ref="B141:B146"/>
+    <mergeCell ref="C141:C146"/>
+    <mergeCell ref="D141:I146"/>
+    <mergeCell ref="A133:I133"/>
+    <mergeCell ref="A134:A139"/>
+    <mergeCell ref="B134:B139"/>
+    <mergeCell ref="C134:C139"/>
+    <mergeCell ref="D134:I139"/>
+    <mergeCell ref="A126:I126"/>
+    <mergeCell ref="A127:A132"/>
+    <mergeCell ref="B127:B132"/>
+    <mergeCell ref="C127:C132"/>
+    <mergeCell ref="D127:I132"/>
+    <mergeCell ref="A119:I119"/>
+    <mergeCell ref="A120:A125"/>
+    <mergeCell ref="B120:B125"/>
+    <mergeCell ref="C120:C125"/>
+    <mergeCell ref="D120:I125"/>
+    <mergeCell ref="A112:I112"/>
+    <mergeCell ref="A113:A118"/>
+    <mergeCell ref="B113:B118"/>
+    <mergeCell ref="C113:C118"/>
+    <mergeCell ref="D113:I118"/>
+    <mergeCell ref="A105:I105"/>
+    <mergeCell ref="A106:A111"/>
+    <mergeCell ref="B106:B111"/>
+    <mergeCell ref="C106:C111"/>
+    <mergeCell ref="D106:I111"/>
+    <mergeCell ref="A98:I98"/>
+    <mergeCell ref="A99:A104"/>
+    <mergeCell ref="B99:B104"/>
+    <mergeCell ref="C99:C104"/>
+    <mergeCell ref="D99:I104"/>
+    <mergeCell ref="A91:I91"/>
+    <mergeCell ref="A92:A97"/>
+    <mergeCell ref="B92:B97"/>
+    <mergeCell ref="C92:C97"/>
+    <mergeCell ref="D92:I97"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A22:A27"/>
@@ -2479,16 +3834,55 @@
     <mergeCell ref="D19:I19"/>
     <mergeCell ref="D20:I20"/>
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A91:I91"/>
-    <mergeCell ref="A92:A97"/>
-    <mergeCell ref="B92:B97"/>
-    <mergeCell ref="C92:C97"/>
-    <mergeCell ref="D92:I97"/>
-    <mergeCell ref="A98:I98"/>
-    <mergeCell ref="A99:A104"/>
-    <mergeCell ref="B99:B104"/>
-    <mergeCell ref="C99:C104"/>
-    <mergeCell ref="D99:I104"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="D22:I27"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="D10:I13"/>
+    <mergeCell ref="A63:I63"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="B64:B69"/>
+    <mergeCell ref="A50:A55"/>
+    <mergeCell ref="B50:B55"/>
+    <mergeCell ref="C50:C55"/>
+    <mergeCell ref="D50:I55"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A57:A62"/>
+    <mergeCell ref="B57:B62"/>
+    <mergeCell ref="C57:C62"/>
+    <mergeCell ref="D57:I62"/>
+    <mergeCell ref="C64:C69"/>
+    <mergeCell ref="D64:I69"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A78:A83"/>
+    <mergeCell ref="B78:B83"/>
+    <mergeCell ref="C78:C83"/>
+    <mergeCell ref="D78:I83"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="A85:A90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C85:C90"/>
+    <mergeCell ref="D85:I90"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B43:B48"/>
+    <mergeCell ref="C43:C48"/>
+    <mergeCell ref="D43:I48"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="D36:I41"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A29:A34"/>
+    <mergeCell ref="B29:B34"/>
+    <mergeCell ref="C29:C34"/>
+    <mergeCell ref="D29:I34"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="C71:C76"/>
+    <mergeCell ref="D71:I76"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="37" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
